--- a/artfynd/A 16422-2023 artfynd.xlsx
+++ b/artfynd/A 16422-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133587823</v>
       </c>
       <c r="B2" t="n">
-        <v>96487</v>
+        <v>96494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133587824</v>
       </c>
       <c r="B3" t="n">
-        <v>97875</v>
+        <v>97882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>133587821</v>
       </c>
       <c r="B4" t="n">
-        <v>96498</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>133587827</v>
       </c>
       <c r="B5" t="n">
-        <v>96498</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>133587826</v>
       </c>
       <c r="B6" t="n">
-        <v>96500</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16422-2023 artfynd.xlsx
+++ b/artfynd/A 16422-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133587823</v>
+        <v>133587824</v>
       </c>
       <c r="B2" t="n">
-        <v>96494</v>
+        <v>97889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2605</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stenporella</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porella cordaeana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Huebener) Moore</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Backen, ca 1,3 km SV om, Dls</t>
+          <t>Södra Backen, ca 1,2 km SV om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334398</v>
+        <v>334545</v>
       </c>
       <c r="R2" t="n">
-        <v>6541233</v>
+        <v>6541295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,12 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lodyta i äldre blandskog.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sten.</t>
+          <t>Bergvägg, lodyta vid medelålders granplantering</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133587824</v>
+        <v>133587826</v>
       </c>
       <c r="B3" t="n">
-        <v>97882</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2605</v>
+        <v>2666</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stenporella</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella cordaeana</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huebener) Moore</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,7 +882,7 @@
         <v>133587821</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +984,7 @@
         <v>133587827</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133587826</v>
+        <v>133587823</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2666</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Backen, ca 1,2 km SV om, Dls</t>
+          <t>Södra Backen, ca 1,3 km SV om, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334545</v>
+        <v>334398</v>
       </c>
       <c r="R6" t="n">
-        <v>6541295</v>
+        <v>6541233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1167,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bergvägg, lodyta vid medelålders granplantering</t>
+          <t>Lodyta i äldre blandskog.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sten.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1187,6 +1187,215 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133587817</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Backen, ca 1,2 km SV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334601</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6541327</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Sumpskog, frodig mark vid bäck.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133587818</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Backen, ca 1,2 km SV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334580</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6541329</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Större sälg i bergbrant.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bergbrant, lodyta med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16422-2023 artfynd.xlsx
+++ b/artfynd/A 16422-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587824</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587826</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587821</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587823</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587817</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,8 +1431,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133587818</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>